--- a/dcf/ZS.xlsx
+++ b/dcf/ZS.xlsx
@@ -361,77 +361,77 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>builder default — last-year capex +10% unless set to guidance; edits not tracked</t>
+        <t>workbook (synced) — last-year capex +10% unless set to guidance; edits not tracked</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>Opus: 22.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -867,7 +867,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>builder defaults (consensus-anchored; no Opus pass)</t>
+          <t>Opus 4.8 — values as of 2026-07-06 (provenance seeded)</t>
         </is>
       </c>
     </row>
@@ -1122,184 +1122,184 @@
     </row>
     <row r="5">
       <c r="A5" s="52" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>25.1937086513372</v>
+        <v>46.24315580726847</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>24.38580873573451</v>
+        <v>44.47434547511463</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>23.62052209497553</v>
+        <v>42.79618067773267</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>22.89548345752987</v>
+        <v>41.20368881367319</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>22.20846756759286</v>
+        <v>39.69218993228106</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>21.55738034298735</v>
+        <v>38.25727831217107</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>20.94025062716903</v>
+        <v>36.89480527507337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>27.29865336693032</v>
+        <v>48.34810052286159</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>26.39466240967253</v>
+        <v>46.48319914905265</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>25.53808795325125</v>
+        <v>44.71374653600839</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>24.72630399314421</v>
+        <v>43.03450934928752</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>23.95683980406168</v>
+        <v>41.44056216874989</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>23.22737013990572</v>
+        <v>39.92726810908944</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>22.53570609195947</v>
+        <v>38.49026073986381</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="52" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>29.40359808252345</v>
+        <v>50.45304523845472</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>28.40351608361053</v>
+        <v>48.49205282299066</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>27.45565381152696</v>
+        <v>46.63131239428409</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>26.55712452875854</v>
+        <v>44.86532988490185</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>25.7052120405305</v>
+        <v>43.1889344052187</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>24.8973599368241</v>
+        <v>41.59725790600781</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>24.1311615567499</v>
+        <v>40.08571620465425</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>31.50854279811658</v>
+        <v>52.55798995404783</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>30.41236975754855</v>
+        <v>50.50090649692866</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>29.37321966980267</v>
+        <v>48.5488782525598</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>28.38794506437288</v>
+        <v>46.69615042051619</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>27.45358427699933</v>
+        <v>44.93730664168752</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>26.56734973374247</v>
+        <v>43.26724770292618</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>25.72661702154033</v>
+        <v>41.68117166944469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>33.6134875137097</v>
+        <v>54.66293466964097</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>32.42122343148656</v>
+        <v>52.50976017086669</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>31.29078552807839</v>
+        <v>50.46644411083552</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>30.2187655999872</v>
+        <v>48.52697095613051</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>29.20195651346815</v>
+        <v>46.68567887815635</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>28.23733953066084</v>
+        <v>44.93723749984455</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>27.32207248633078</v>
+        <v>43.27662713423512</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>35.71843222930283</v>
+        <v>56.7678793852341</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>34.43007710542458</v>
+        <v>54.51861384480469</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>33.2083513863541</v>
+        <v>52.38400996911124</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>32.04958613560154</v>
+        <v>50.35779149174485</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>30.95032874993696</v>
+        <v>48.43405111462517</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>29.90732932757921</v>
+        <v>46.60722729676292</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>28.9175279511212</v>
+        <v>44.87208259902556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>37.82337694489596</v>
+        <v>58.87282410082722</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>36.43893077936259</v>
+        <v>56.5274675187427</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>35.12591724462982</v>
+        <v>54.30157582738695</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>33.88040667121586</v>
+        <v>52.18861202735918</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>32.69870098640578</v>
+        <v>50.18242335109399</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>31.57731912449759</v>
+        <v>48.2772170936813</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>30.51298341591164</v>
+        <v>46.467538063816</v>
       </c>
     </row>
     <row r="13">
@@ -1322,7 +1322,7 @@
         <v>0.0825939236163287</v>
       </c>
       <c r="C14" s="56" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.3443223402301003</v>
+        <v>0.3455689296121305</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24369,7 +24369,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>28.38794506437288</v>
+        <v>46.69615042051619</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>48.03889354184415</v>
+        <v>75.36655047555509</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>15.26287342426058</v>
+        <v>26.70511510805951</v>
       </c>
     </row>
     <row r="59">
@@ -24733,7 +24733,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>no Opus assumptions file — every input is a builder default</t>
+          <t>seeded 2026-07-06 from the synced assumptions block (pass predates provenance tracking — may already include your edits)</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -24806,7 +24806,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="31" t="inlineStr"/>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24825,7 +24829,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -24833,7 +24837,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr"/>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24852,7 +24860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -24860,7 +24868,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr"/>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24879,7 +24891,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -24887,7 +24899,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24906,7 +24922,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -24914,7 +24930,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr"/>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24933,7 +24953,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -24941,7 +24961,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr"/>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24960,7 +24984,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -24968,7 +24992,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr"/>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24987,7 +25015,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -24995,7 +25023,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr"/>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25014,7 +25046,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -25022,7 +25054,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr"/>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25041,7 +25077,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25049,7 +25085,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr"/>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25068,7 +25108,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -25076,7 +25116,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr"/>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25095,7 +25139,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -25103,7 +25147,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25122,12 +25170,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>Opus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.0x</t>
         </is>
       </c>
       <c r="F20" s="31" t="inlineStr"/>
@@ -25149,7 +25197,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -25157,7 +25205,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="31" t="inlineStr"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25176,7 +25228,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/dcf/ZS.xlsx
+++ b/dcf/ZS.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.0675939236163287</v>
+        <v>0.0677334216646617</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.0725939236163287</v>
+        <v>0.07273342166466171</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07759392361632869</v>
+        <v>0.0777334216646617</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.0825939236163287</v>
+        <v>0.0827334216646617</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.0875939236163287</v>
+        <v>0.08773342166466171</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.09259392361632869</v>
+        <v>0.0927334216646617</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.0975939236163287</v>
+        <v>0.0977334216646617</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>46.24315580726847</v>
+        <v>39.61619248133672</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>44.47434547511463</v>
+        <v>38.15719594915357</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>42.79618067773267</v>
+        <v>36.77319497484943</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>41.20368881367319</v>
+        <v>35.46007124328508</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>39.69218993228106</v>
+        <v>34.21394891057415</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>38.25727831217107</v>
+        <v>33.03117933892243</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>36.89480527507337</v>
+        <v>31.90832685520274</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>48.34810052286159</v>
+        <v>41.3623711150507</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>46.48319914905265</v>
+        <v>39.82367141594253</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>44.71374653600839</v>
+        <v>38.36395082818635</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>43.03450934928752</v>
+        <v>36.97887482512628</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>41.44056216874989</v>
+        <v>35.66436400695571</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>39.92726810908944</v>
+        <v>34.41657804138643</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>38.49026073986381</v>
+        <v>33.23190068121039</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>50.45304523845472</v>
+        <v>43.10854974876467</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>48.49205282299066</v>
+        <v>41.49014688273149</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>46.63131239428409</v>
+        <v>39.95470668152326</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>44.86532988490185</v>
+        <v>38.49767840696748</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>43.1889344052187</v>
+        <v>37.11477910333725</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>41.59725790600781</v>
+        <v>35.80197674385042</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>40.08571620465425</v>
+        <v>34.55547450721803</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>52.55798995404783</v>
+        <v>44.85472838247865</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>50.50090649692866</v>
+        <v>43.15662234952048</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>48.5488782525598</v>
+        <v>41.54546253486017</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>46.69615042051619</v>
+        <v>40.01648198880868</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>44.93730664168752</v>
+        <v>38.5651941997188</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>43.26724770292618</v>
+        <v>37.18737544631442</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>41.68117166944469</v>
+        <v>35.8790483332257</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>54.66293466964097</v>
+        <v>46.60090701619263</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>52.50976017086669</v>
+        <v>44.82309781630944</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>50.46644411083552</v>
+        <v>43.1362183881971</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>48.52697095613051</v>
+        <v>41.53528557064988</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>46.68567887815635</v>
+        <v>40.01560929610036</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>44.93723749984455</v>
+        <v>38.57277414877841</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>43.27662713423512</v>
+        <v>37.20262215923335</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>56.7678793852341</v>
+        <v>48.3470856499066</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>54.51861384480469</v>
+        <v>46.4895732830984</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>52.38400996911124</v>
+        <v>44.726974241534</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>50.35779149174485</v>
+        <v>43.05408915249109</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>48.43405111462517</v>
+        <v>41.46602439248191</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>46.60722729676292</v>
+        <v>39.95817285124242</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>44.87208259902556</v>
+        <v>38.526195985241</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>58.87282410082722</v>
+        <v>50.09326428362058</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>56.5274675187427</v>
+        <v>48.15604874988737</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>54.30157582738695</v>
+        <v>46.31773009487093</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>52.18861202735918</v>
+        <v>44.57289273433229</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>50.18242335109399</v>
+        <v>42.91643948886347</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>48.2772170936813</v>
+        <v>41.34357155370643</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>46.467538063816</v>
+        <v>39.84976981124866</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>147.3300018310547</v>
+        <v>153.5500030517578</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.0825939236163287</v>
+        <v>0.0827334216646617</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>22</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.3455689296121305</v>
+        <v>0.3512342845222662</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>147.3300018310547</v>
+        <v>153.5500030517578</v>
       </c>
     </row>
     <row r="49">
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>46.69615042051619</v>
+        <v>40.01648198880868</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>75.36655047555509</v>
+        <v>62.70256029007701</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>26.70511510805951</v>
+        <v>23.68486826623935</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/ZS.xlsx
+++ b/dcf/ZS.xlsx
@@ -1125,25 +1125,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>39.61619248133672</v>
+        <v>121.5199434872369</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>38.15719594915357</v>
+        <v>116.6674660358785</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>36.77319497484943</v>
+        <v>112.0524179177182</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>35.46007124328508</v>
+        <v>107.6620774908924</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>34.21394891057415</v>
+        <v>103.4844613529503</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>33.03117933892243</v>
+        <v>99.50827829976755</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>31.90832685520274</v>
+        <v>95.72288635191913</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>41.3623711150507</v>
+        <v>126.4960000939342</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>39.82367141594253</v>
+        <v>121.4163938353081</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>38.36395082818635</v>
+        <v>116.5855687768623</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>36.97887482512628</v>
+        <v>111.9901871423214</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>35.66436400695571</v>
+        <v>107.6176854592677</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>34.41657804138643</v>
+        <v>103.4562262549222</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>33.23190068121039</v>
+        <v>99.49465297086397</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>43.10854974876467</v>
+        <v>131.4720567006316</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>41.49014688273149</v>
+        <v>126.1653216347377</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>39.95470668152326</v>
+        <v>121.1187196360065</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>38.49767840696748</v>
+        <v>116.3182967937504</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>37.11477910333725</v>
+        <v>111.7509095655852</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>35.80197674385042</v>
+        <v>107.4041742100769</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>34.55547450721803</v>
+        <v>103.2664195898088</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>44.85472838247865</v>
+        <v>136.4481133073289</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>43.15662234952048</v>
+        <v>130.9142494341673</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>41.54546253486017</v>
+        <v>125.6518704951506</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>40.01648198880868</v>
+        <v>120.6464064451793</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>38.5651941997188</v>
+        <v>115.8841336719026</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>37.18737544631442</v>
+        <v>111.3521221652316</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>35.8790483332257</v>
+        <v>107.0381862087536</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>46.60090701619263</v>
+        <v>141.4241699140263</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>44.82309781630944</v>
+        <v>135.6631772335969</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>43.1362183881971</v>
+        <v>130.1850213542948</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>41.53528557064988</v>
+        <v>124.9745160966083</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>40.01560929610036</v>
+        <v>120.01735777822</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>38.57277414877841</v>
+        <v>115.3000701203864</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>37.20262215923335</v>
+        <v>110.8099528276985</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>48.3470856499066</v>
+        <v>146.4002265207236</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>46.4895732830984</v>
+        <v>140.4121050330265</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>44.726974241534</v>
+        <v>134.7181722134389</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>43.05408915249109</v>
+        <v>129.3026257480373</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>41.46602439248191</v>
+        <v>124.1505818845374</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>39.95817285124242</v>
+        <v>119.2480180755411</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>38.526195985241</v>
+        <v>114.5817194466433</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>50.09326428362058</v>
+        <v>151.376283127421</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>48.15604874988737</v>
+        <v>145.1610328324561</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>46.31773009487093</v>
+        <v>139.2513230725831</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>44.57289273433229</v>
+        <v>133.6307353994663</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>42.91643948886347</v>
+        <v>128.2838059908548</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>41.34357155370643</v>
+        <v>123.1959660306958</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>39.84976981124866</v>
+        <v>118.3534860655882</v>
       </c>
     </row>
     <row r="13">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.3512342845222662</v>
+        <v>0.7385726024960255</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24209,7 +24209,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.1821846165275594</v>
+        <v>0.28</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>40.01648198880868</v>
+        <v>120.6464064451793</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>62.70256029007701</v>
+        <v>162.1520650845187</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>23.68486826623935</v>
+        <v>88.70925409457938</v>
       </c>
     </row>
     <row r="59">
@@ -24642,7 +24642,7 @@
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>0.2474079865624935</v>
+        <v>0.2</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>0.1484447919374961</v>
+        <v>0.1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
